--- a/data/trans_orig/P42-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P42-Provincia-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>190919</t>
+          <t>190103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218322</t>
+          <t>217944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190919</t>
+          <t>190103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218322</t>
+          <t>217944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69919</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69919</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>391931</t>
+          <t>391222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>425958</t>
+          <t>425245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>391931</t>
+          <t>391222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>425958</t>
+          <t>425245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>76624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>110647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>76624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>110647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237768</t>
+          <t>236847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267438</t>
+          <t>267241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>237768</t>
+          <t>236847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267438</t>
+          <t>267241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>66289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95762</t>
+          <t>96683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>66289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95762</t>
+          <t>96683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267337</t>
+          <t>264272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298278</t>
+          <t>296293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>267337</t>
+          <t>264272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>298278</t>
+          <t>296293</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72062</t>
+          <t>74047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103003</t>
+          <t>106068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72062</t>
+          <t>74047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103003</t>
+          <t>106068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135897</t>
+          <t>136429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161578</t>
+          <t>160561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135897</t>
+          <t>136429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161578</t>
+          <t>160561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67469</t>
+          <t>66937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67469</t>
+          <t>66937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>188865</t>
+          <t>187997</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217036</t>
+          <t>217592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188865</t>
+          <t>187997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>217036</t>
+          <t>217592</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>59381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88108</t>
+          <t>88976</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>59381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88108</t>
+          <t>88976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>514651</t>
+          <t>514684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>551646</t>
+          <t>551367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>514651</t>
+          <t>514684</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>551646</t>
+          <t>551367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86573</t>
+          <t>86852</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>123535</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86573</t>
+          <t>86852</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>123535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>598361</t>
+          <t>598041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>643566</t>
+          <t>643712</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>598361</t>
+          <t>598041</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>643566</t>
+          <t>643712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>135397</t>
+          <t>135251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>180602</t>
+          <t>180922</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>135397</t>
+          <t>135251</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>180602</t>
+          <t>180922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>238067</t>
+          <t>237761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>260644</t>
+          <t>261183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238067</t>
+          <t>237761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>260644</t>
+          <t>261183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>459693</t>
+          <t>458910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>486897</t>
+          <t>486007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>459693</t>
+          <t>458910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>486897</t>
+          <t>486007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>63863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>63863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>276816</t>
+          <t>276725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>303724</t>
+          <t>303337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>276816</t>
+          <t>276725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303724</t>
+          <t>303337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63162</t>
+          <t>63253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63162</t>
+          <t>63253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>313032</t>
+          <t>311274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>341144</t>
+          <t>341655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>313032</t>
+          <t>311274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>341144</t>
+          <t>341655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>46319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74942</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>46319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74942</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175921</t>
+          <t>176946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197068</t>
+          <t>197673</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175921</t>
+          <t>176946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197068</t>
+          <t>197673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>42645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22523</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>42645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>227138</t>
+          <t>228005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>251830</t>
+          <t>251466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227138</t>
+          <t>228005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>251830</t>
+          <t>251466</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52893</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52893</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>601833</t>
+          <t>600516</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>634631</t>
+          <t>634166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>601833</t>
+          <t>600516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>634631</t>
+          <t>634166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88881</t>
+          <t>90198</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88881</t>
+          <t>90198</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>670582</t>
+          <t>670621</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>710006</t>
+          <t>710903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>670582</t>
+          <t>670621</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>710006</t>
+          <t>710903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102006</t>
+          <t>101109</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>141430</t>
+          <t>141391</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102006</t>
+          <t>101109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141430</t>
+          <t>141391</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3041580</t>
+          <t>3039240</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3124401</t>
+          <t>3120170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3041580</t>
+          <t>3039240</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3124401</t>
+          <t>3120170</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>412792</t>
+          <t>417023</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>495613</t>
+          <t>497953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>412792</t>
+          <t>417023</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>495613</t>
+          <t>497953</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5307,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>227034</t>
+          <t>226670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249742</t>
+          <t>250888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227034</t>
+          <t>226670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>249742</t>
+          <t>250888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>54984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>54984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>418697</t>
+          <t>419657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>453440</t>
+          <t>454153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>418697</t>
+          <t>419657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>453440</t>
+          <t>454153</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65779</t>
+          <t>65066</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100522</t>
+          <t>99562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65779</t>
+          <t>65066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100522</t>
+          <t>99562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -5783,12 +5783,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>274880</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>301177</t>
+          <t>301229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>274880</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>301177</t>
+          <t>301229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59435</t>
+          <t>58174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59435</t>
+          <t>58174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>311711</t>
+          <t>312012</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>341522</t>
+          <t>340933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311711</t>
+          <t>312012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>341522</t>
+          <t>340933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74648</t>
+          <t>74347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74648</t>
+          <t>74347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185847</t>
+          <t>185483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202570</t>
+          <t>202925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185847</t>
+          <t>185483</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>202570</t>
+          <t>202925</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31872</t>
+          <t>32236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31872</t>
+          <t>32236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -6497,12 +6497,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>201040</t>
+          <t>201051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>227402</t>
+          <t>227428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>201040</t>
+          <t>201051</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>227402</t>
+          <t>227428</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6575,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72075</t>
+          <t>72064</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72075</t>
+          <t>72064</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>610220</t>
+          <t>611901</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>642488</t>
+          <t>642003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>610220</t>
+          <t>611901</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>642488</t>
+          <t>642003</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42362</t>
+          <t>42847</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74630</t>
+          <t>72949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42362</t>
+          <t>42847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74630</t>
+          <t>72949</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -6973,12 +6973,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>716925</t>
+          <t>717087</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>752299</t>
+          <t>751340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>716925</t>
+          <t>717087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>752299</t>
+          <t>751340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>67564</t>
+          <t>68523</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102938</t>
+          <t>102776</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67564</t>
+          <t>68523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102938</t>
+          <t>102776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3023913</t>
+          <t>3023962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3102832</t>
+          <t>3105291</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3023913</t>
+          <t>3023962</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3102832</t>
+          <t>3105291</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>414263</t>
+          <t>411804</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>493182</t>
+          <t>493133</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>414263</t>
+          <t>411804</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>493182</t>
+          <t>493133</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7619,32 +7619,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>174526</t>
+          <t>192811</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>157392</t>
+          <t>182554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181083</t>
+          <t>197802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7654,32 +7654,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>174526</t>
+          <t>192811</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157392</t>
+          <t>182554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181083</t>
+          <t>197802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -7697,32 +7697,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -7775,17 +7775,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7810,17 +7810,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>367710</t>
+          <t>387540</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>351742</t>
+          <t>370819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>378328</t>
+          <t>399119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>367710</t>
+          <t>387540</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>351742</t>
+          <t>370819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>378328</t>
+          <t>399119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -7935,32 +7935,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54412</t>
+          <t>60839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7970,32 +7970,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54412</t>
+          <t>60839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -8013,17 +8013,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>406154</t>
+          <t>431658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>406154</t>
+          <t>431658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>406154</t>
+          <t>431658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8048,17 +8048,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>406154</t>
+          <t>431658</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>406154</t>
+          <t>431658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>406154</t>
+          <t>431658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8095,32 +8095,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>201294</t>
+          <t>205331</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187686</t>
+          <t>191099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213684</t>
+          <t>216585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8130,32 +8130,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>201294</t>
+          <t>205331</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187686</t>
+          <t>191099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>213684</t>
+          <t>216585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -8173,32 +8173,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49870</t>
+          <t>50085</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63478</t>
+          <t>64317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8208,32 +8208,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49870</t>
+          <t>50085</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63478</t>
+          <t>64317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -8251,17 +8251,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>251164</t>
+          <t>255416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>251164</t>
+          <t>255416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>251164</t>
+          <t>255416</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8286,17 +8286,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>251164</t>
+          <t>255416</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>251164</t>
+          <t>255416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251164</t>
+          <t>255416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8333,32 +8333,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>353337</t>
+          <t>282580</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>333962</t>
+          <t>265773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>369450</t>
+          <t>295236</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>353337</t>
+          <t>282580</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>333962</t>
+          <t>265773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>369450</t>
+          <t>295236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -8411,32 +8411,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31920</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51295</t>
+          <t>54787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8446,32 +8446,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31920</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51295</t>
+          <t>54787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -8489,17 +8489,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>385257</t>
+          <t>320560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>385257</t>
+          <t>320560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>385257</t>
+          <t>320560</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>385257</t>
+          <t>320560</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>385257</t>
+          <t>320560</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>385257</t>
+          <t>320560</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8571,32 +8571,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>131587</t>
+          <t>142451</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123609</t>
+          <t>133330</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136817</t>
+          <t>149494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8606,32 +8606,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>131587</t>
+          <t>142451</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123609</t>
+          <t>133330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136817</t>
+          <t>149494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -8649,32 +8649,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28649</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8684,32 +8684,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28649</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -8727,17 +8727,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>166513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>166513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>166513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8762,17 +8762,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>166513</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>166513</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>166513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>147981</t>
+          <t>153419</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>136780</t>
+          <t>142378</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>158736</t>
+          <t>164907</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,32 +8844,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>147981</t>
+          <t>153419</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>136780</t>
+          <t>142378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>158736</t>
+          <t>164907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -8887,32 +8887,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>61843</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>50525</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73044</t>
+          <t>73054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8922,32 +8922,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61843</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>50525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73044</t>
+          <t>73054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -8965,17 +8965,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9047,32 +9047,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>393933</t>
+          <t>468244</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173554</t>
+          <t>447827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>579370</t>
+          <t>482441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9082,32 +9082,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>393933</t>
+          <t>468244</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173554</t>
+          <t>447827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>579370</t>
+          <t>482441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -9125,32 +9125,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>263279</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>77842</t>
+          <t>53361</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>483658</t>
+          <t>87975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9160,32 +9160,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>263279</t>
+          <t>67558</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77842</t>
+          <t>53361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>483658</t>
+          <t>87975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -9203,17 +9203,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>657212</t>
+          <t>535802</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>657212</t>
+          <t>535802</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>657212</t>
+          <t>535802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>657212</t>
+          <t>535802</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>657212</t>
+          <t>535802</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>657212</t>
+          <t>535802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9285,32 +9285,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>449745</t>
+          <t>511400</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>428759</t>
+          <t>485975</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>468209</t>
+          <t>532796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9320,32 +9320,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>449745</t>
+          <t>511400</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>428759</t>
+          <t>485975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>468209</t>
+          <t>532796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -9363,32 +9363,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>128472</t>
+          <t>159241</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>137845</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149458</t>
+          <t>184666</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9398,32 +9398,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>128472</t>
+          <t>159241</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>137845</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149458</t>
+          <t>184666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -9441,17 +9441,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9476,17 +9476,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1720767</t>
+          <t>2301184</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2411873</t>
+          <t>2381376</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1720767</t>
+          <t>2301184</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2411873</t>
+          <t>2381376</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>414425</t>
+          <t>418398</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1105531</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>414425</t>
+          <t>418398</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1105531</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -9679,17 +9679,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9714,17 +9714,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
